--- a/calibration/phase2_bayesian_regression/owner_group/EH/EH_prob_metrics.xlsx
+++ b/calibration/phase2_bayesian_regression/owner_group/EH/EH_prob_metrics.xlsx
@@ -115,44 +115,52 @@
     <t>platt</t>
   </si>
   <si>
-    <t>{'coef': 1.200975031380301, 'intercept': -0.12058496027286295, 'C': 1.0}</t>
-  </si>
-  <si>
-    <t>{'coef': 0.9766767604948582, 'intercept': -0.5362615200141656, 'C': 1.0}</t>
-  </si>
-  <si>
-    <t>[0.20673088 0.12002885 0.25088754 0.18595165 0.26721427 0.16414184
- 0.30232186 0.35889123 0.23426515 0.19071838 0.26189809 0.19256613
- 0.16963087 0.31106094 0.29303455 0.40120573 0.22403016 0.56694023
- 0.29018373 0.24956483 0.32264602 0.38205559 0.25482155 0.21823816
- 0.32218519 0.24509114 0.25954937 0.17340501 0.25954937 0.46933871
- 0.12719084 0.18006283 0.47194553 0.27808011 0.71414388 0.29242191
- 0.23386475 0.241739   0.21653915 0.58702545 0.3012528  0.19733783
- 0.24009235 0.37668278 0.2003799  0.1905357  0.25332313 0.26061121
- 0.31502708 0.20375245 0.1404666  0.24702976 0.22203141 0.08147695
- 0.45366585 0.27572496 0.36144127 0.24882002 0.18062682 0.34082316
- 0.26870959 0.19651622 0.33024732 0.32883557 0.13605298 0.31984168
- 0.37231719 0.15954138 0.32268022 0.40365486 0.41415183 0.19399984
- 0.22515157 0.27398841 0.21824591 0.24894521 0.25863084 0.42318567
- 0.28390999 0.18631564 0.43834988 0.53967282 0.18490439 0.22794847
- 0.22911763 0.23647246]</t>
-  </si>
-  <si>
-    <t>[0.23461585 0.16311352 0.20932133 0.24675123 0.39666095 0.16819179
- 0.46566093 0.30688226 0.22898892 0.20784649 0.22898892 0.36939982
- 0.22569512 0.18122986 0.6204698  0.28298038 0.48157915 0.24546723
- 0.22152075 0.2274919  0.11488929 0.35586253 0.13491224 0.21547702
- 0.27937552 0.25543067 0.39305586 0.13876557 0.16378818 0.20487523
- 0.28047198 0.2951014  0.2527704  0.30067873 0.09534153 0.18097173
- 0.23616129 0.3550914  0.15447818 0.23249337 0.25994012 0.27086645
- 0.32002783 0.51090604 0.24000344 0.15211223 0.1443457  0.22690906
- 0.29187405 0.16843851 0.2274919  0.39896122 0.3196875  0.41270557
- 0.42177555 0.20905526 0.3833061  0.10122745 0.39083037 0.24976407
- 0.30951133 0.4216945  0.17146899 0.2619636  0.14572653 0.42056575
- 0.20519279 0.27017686 0.33823985 0.1935803  0.16311352 0.4152559
- 0.2599902  0.1098828  0.30103794 0.2039574  0.19778967 0.25479782
- 0.20082927 0.19488327 0.22951856 0.290869   0.28487715 0.3037235
- 0.12913728 0.43684188 0.0752576 ]</t>
+    <t>{'coef': 0.8598538136971873, 'intercept': -0.37490409315242934, 'C': 1.0}</t>
+  </si>
+  <si>
+    <t>{'coef': 1.398340061736008, 'intercept': -0.2595296694909274, 'C': 1.0}</t>
+  </si>
+  <si>
+    <t>[0.2287502  0.35260536 0.49183777 0.28363091 0.24033493 0.44426748
+ 0.32093886 0.238907   0.25837377 0.37622188 0.20396039 0.22351291
+ 0.35799118 0.31198287 0.33322031 0.29368325 0.25194056 0.23763285
+ 0.31124085 0.3392762  0.33840547 0.34180386 0.29353262 0.52557891
+ 0.4048672  0.24033223 0.22817433 0.41685962 0.19044258 0.37486153
+ 0.29243079 0.28886622 0.26579185 0.30782613 0.29193532 0.25917745
+ 0.22073153 0.50314075 0.27814924 0.23793301 0.32812855 0.5922317
+ 0.21083558 0.29020248 0.33150153 0.26579185 0.20942076 0.32501569
+ 0.30706784 0.30143221 0.30910318 0.27075071 0.30479455 0.2156399
+ 0.22155918 0.28963073 0.33066584 0.41893353 0.3560649  0.31433485
+ 0.3493393  0.35648279 0.23594941 0.16383904 0.25480797 0.17688523
+ 0.23421404 0.22017117 0.28828339 0.31482658 0.25163043 0.23999464
+ 0.29977345 0.21958788 0.20942076 0.27776068 0.29353613 0.3125796
+ 0.3367933  0.2560968  0.40441121 0.30932077 0.24033493 0.33916376
+ 0.33588062 0.2729386  0.23056826 0.31047679 0.28274662 0.29682294
+ 0.21625745 0.29682294 0.41862088 0.17907945 0.25198805 0.39071496
+ 0.3030954  0.53592655 0.28516477 0.27439963 0.22891635 0.27898121
+ 0.37424877 0.30141067 0.23084488 0.24938785 0.2860098  0.26878165
+ 0.24763291 0.2169892  0.25769745]</t>
+  </si>
+  <si>
+    <t>[0.20598772 0.24238934 0.18263245 0.10722072 0.20538366 0.19679439
+ 0.07354183 0.31081173 0.20373859 0.33205172 0.19508289 0.15456139
+ 0.2601313  0.26343834 0.2094418  0.25538084 0.27179733 0.11969857
+ 0.250694   0.25391594 0.15355279 0.25542548 0.39844257 0.2955186
+ 0.42962304 0.1325111  0.18712385 0.27647853 0.20040488 0.13579468
+ 0.25360873 0.21656036 0.35469168 0.18794186 0.33859628 0.13929722
+ 0.30094776 0.06069791 0.37033    0.19471012 0.22599176 0.21459237
+ 0.2336202  0.24830294 0.1692991  0.25414047 0.06415567 0.28763434
+ 0.4079618  0.08897333 0.14097142 0.4467019  0.14229888 0.50949085
+ 0.33299348 0.26818302 0.26818302 0.4285372  0.23587379 0.1563955
+ 0.6877006  0.42695504 0.48179632 0.26222253 0.35286456 0.2730928
+ 0.24021229 0.10613345 0.4583518  0.11603795 0.22003567 0.25681296
+ 0.24238934 0.3805308  0.11674819 0.12800144 0.16726051 0.22606455
+ 0.38093424 0.27046955 0.06478463 0.33249414 0.08017457 0.18335243
+ 0.3131937  0.40173972 0.1409855  0.24032743 0.23522371 0.23235232
+ 0.40314662 0.57714474 0.24882278 0.14591435 0.1326915  0.25315937
+ 0.23819044 0.14461255 0.24021229 0.4524554  0.35329446 0.40617025
+ 0.40729204 0.21588135 0.35424733 0.08076473 0.3314099  0.24179585
+ 0.31505919 0.45434225 0.18240839 0.3483368 ]</t>
   </si>
 </sst>
 </file>
@@ -592,49 +600,49 @@
     </row>
     <row r="2" spans="1:25">
       <c r="A2">
-        <v>86</v>
+        <v>111</v>
       </c>
       <c r="B2">
-        <v>0.2790697674418605</v>
+        <v>0.2972972972972973</v>
       </c>
       <c r="C2">
-        <v>0.1860169619321823</v>
+        <v>0.2042228877544403</v>
       </c>
       <c r="D2">
-        <v>0.2011898323418064</v>
+        <v>0.2089116143170197</v>
       </c>
       <c r="E2">
-        <v>0.07541569190159914</v>
+        <v>0.02244358973486438</v>
       </c>
       <c r="F2">
-        <v>0.5567096655851179</v>
+        <v>0.5970362697637798</v>
       </c>
       <c r="G2">
-        <v>0.07590337877356729</v>
+        <v>0.07068444748182554</v>
       </c>
       <c r="H2">
-        <v>0.296758234500885</v>
+        <v>0.3361616015434265</v>
       </c>
       <c r="I2">
-        <v>0.009679778761334431</v>
+        <v>0.009240947783103314</v>
       </c>
       <c r="J2">
-        <v>0.02197173236226604</v>
+        <v>0.01192319732860273</v>
       </c>
       <c r="K2">
-        <v>0.2011898323418064</v>
+        <v>0.2089116143170197</v>
       </c>
       <c r="L2">
-        <v>0.6535618279569891</v>
+        <v>0.6163558663558664</v>
       </c>
       <c r="M2">
-        <v>0.4984539981875689</v>
+        <v>0.4359683429388287</v>
       </c>
       <c r="N2">
-        <v>0.2115342170000076</v>
+        <v>0.2216529548168182</v>
       </c>
       <c r="O2">
-        <v>0.09837976843118668</v>
+        <v>0.09460324048995972</v>
       </c>
       <c r="P2">
         <v>10</v>
@@ -657,49 +665,49 @@
     </row>
     <row r="3" spans="1:25">
       <c r="A3">
-        <v>86</v>
+        <v>111</v>
       </c>
       <c r="B3">
-        <v>0.2790697674418605</v>
+        <v>0.2972972972972973</v>
       </c>
       <c r="C3">
-        <v>0.182449871075665</v>
+        <v>0.2004245227417432</v>
       </c>
       <c r="D3">
-        <v>0.2011898323418064</v>
+        <v>0.2089116143170197</v>
       </c>
       <c r="E3">
-        <v>0.09314566769111643</v>
+        <v>0.04062527400892857</v>
       </c>
       <c r="F3">
-        <v>0.5467610151250323</v>
+        <v>0.5884307676532543</v>
       </c>
       <c r="G3">
-        <v>0.07426636495854848</v>
+        <v>0.0402745396962418</v>
       </c>
       <c r="H3">
-        <v>0.4354538335037877</v>
+        <v>0.2107805234547779</v>
       </c>
       <c r="I3">
-        <v>0.01267482438747772</v>
+        <v>0.004562704538070053</v>
       </c>
       <c r="J3">
-        <v>0.03208793515698385</v>
+        <v>0.01376318720137949</v>
       </c>
       <c r="K3">
-        <v>0.2011898323418064</v>
+        <v>0.2089116143170197</v>
       </c>
       <c r="L3">
-        <v>0.6535618279569891</v>
+        <v>0.6163558663558664</v>
       </c>
       <c r="M3">
-        <v>0.4984539981875689</v>
+        <v>0.4359683429388287</v>
       </c>
       <c r="N3">
-        <v>0.189308422139191</v>
+        <v>0.2031148753838732</v>
       </c>
       <c r="O3">
-        <v>0.1090878631418163</v>
+        <v>0.07618100278553266</v>
       </c>
       <c r="P3">
         <v>10</v>
@@ -728,49 +736,49 @@
     </row>
     <row r="4" spans="1:25">
       <c r="A4">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="B4">
-        <v>0.264367816091954</v>
+        <v>0.2410714285714286</v>
       </c>
       <c r="C4">
-        <v>0.1979968398809433</v>
+        <v>0.1886982917785645</v>
       </c>
       <c r="D4">
-        <v>0.1944774739067248</v>
+        <v>0.1829559948979592</v>
       </c>
       <c r="E4">
-        <v>-0.0180965224584646</v>
+        <v>-0.03138621876702063</v>
       </c>
       <c r="F4">
-        <v>0.5804508230886049</v>
+        <v>0.5616011829219087</v>
       </c>
       <c r="G4">
-        <v>0.1071675423232988</v>
+        <v>0.1112924211525491</v>
       </c>
       <c r="H4">
-        <v>0.7412256598472595</v>
+        <v>0.2097953355312348</v>
       </c>
       <c r="I4">
-        <v>0.01860571378866142</v>
+        <v>0.01592673611900848</v>
       </c>
       <c r="J4">
-        <v>0.01476004095653323</v>
+        <v>0.01041800097698654</v>
       </c>
       <c r="K4">
-        <v>0.1944774739067248</v>
+        <v>0.1829559948979592</v>
       </c>
       <c r="L4">
-        <v>0.6355298913043479</v>
+        <v>0.6191721132897603</v>
       </c>
       <c r="M4">
-        <v>0.3779588578131403</v>
+        <v>0.3544473292371924</v>
       </c>
       <c r="N4">
-        <v>0.2174346894025803</v>
+        <v>0.2180299758911133</v>
       </c>
       <c r="O4">
-        <v>0.1234164834022522</v>
+        <v>0.1008642539381981</v>
       </c>
       <c r="P4">
         <v>10</v>
@@ -793,49 +801,49 @@
     </row>
     <row r="5" spans="1:25">
       <c r="A5">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="B5">
-        <v>0.264367816091954</v>
+        <v>0.2410714285714286</v>
       </c>
       <c r="C5">
-        <v>0.187138631939888</v>
+        <v>0.1782374680042267</v>
       </c>
       <c r="D5">
-        <v>0.1944774739067248</v>
+        <v>0.1829559948979592</v>
       </c>
       <c r="E5">
-        <v>0.03773620573844272</v>
+        <v>0.02579050167973007</v>
       </c>
       <c r="F5">
-        <v>0.5542860796400302</v>
+        <v>0.5339048983958631</v>
       </c>
       <c r="G5">
-        <v>0.06171478176939078</v>
+        <v>0.05505666376224587</v>
       </c>
       <c r="H5">
-        <v>0.6204698085784912</v>
+        <v>0.687700629234314</v>
       </c>
       <c r="I5">
-        <v>0.01041355831989218</v>
+        <v>0.01319149578569506</v>
       </c>
       <c r="J5">
-        <v>0.0176128986755434</v>
+        <v>0.01687669421525318</v>
       </c>
       <c r="K5">
-        <v>0.1944774739067248</v>
+        <v>0.1829559948979592</v>
       </c>
       <c r="L5">
-        <v>0.6355298913043479</v>
+        <v>0.6191721132897603</v>
       </c>
       <c r="M5">
-        <v>0.3779588578131403</v>
+        <v>0.3544473292371924</v>
       </c>
       <c r="N5">
-        <v>0.1829812377691269</v>
+        <v>0.1778344064950943</v>
       </c>
       <c r="O5">
-        <v>0.1031615361571312</v>
+        <v>0.1157295554876328</v>
       </c>
       <c r="P5">
         <v>10</v>
